--- a/artfynd/A 2441-2025 artfynd.xlsx
+++ b/artfynd/A 2441-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56578756</v>
+        <v>62303361</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gålsjö 4350/9750, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506119.9256153756</v>
+        <v>506120</v>
       </c>
       <c r="R2" t="n">
-        <v>6532160.917515481</v>
+        <v>6532161</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1960-07-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1964-07-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1960-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1964-07-10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Häggen, i gamla floror. Riklig</t>
+          <t>Häggen, i gamla floror</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +789,7 @@
         <v>62081982</v>
       </c>
       <c r="B3" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506119.9256153756</v>
+        <v>506120</v>
       </c>
       <c r="R3" t="n">
-        <v>6532160.917515481</v>
+        <v>6532161</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +854,9 @@
           <t>1960-07-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1960-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,12 +896,7 @@
         <v>62082464</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506119.9256153756</v>
+        <v>506120</v>
       </c>
       <c r="R4" t="n">
-        <v>6532160.917515481</v>
+        <v>6532161</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -992,19 +961,9 @@
           <t>1960-07-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1960-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62303361</v>
+        <v>56578756</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,38 +1011,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gålsjö 4350/9750, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506119.9256153756</v>
+        <v>506120</v>
       </c>
       <c r="R5" t="n">
-        <v>6532160.917515481</v>
+        <v>6532161</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1115,27 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1964-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1960-07-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1964-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1960-07-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Häggen, i gamla floror</t>
+          <t>Häggen, i gamla floror. Riklig</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2441-2025 artfynd.xlsx
+++ b/artfynd/A 2441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62303361</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62081982</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082464</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,8 +1124,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56578756</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>